--- a/artfynd/A 16206-2022 artfynd.xlsx
+++ b/artfynd/A 16206-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 16206-2022 artfynd.xlsx
+++ b/artfynd/A 16206-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1360,6 +1360,103 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127691224</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91295</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>I20-skogen, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>759417</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7091029</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Umeå stad</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16206-2022 artfynd.xlsx
+++ b/artfynd/A 16206-2022 artfynd.xlsx
@@ -1365,7 +1365,7 @@
         <v>127691224</v>
       </c>
       <c r="B8" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 16206-2022 artfynd.xlsx
+++ b/artfynd/A 16206-2022 artfynd.xlsx
@@ -1365,7 +1365,7 @@
         <v>127691224</v>
       </c>
       <c r="B8" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 16206-2022 artfynd.xlsx
+++ b/artfynd/A 16206-2022 artfynd.xlsx
@@ -1365,7 +1365,7 @@
         <v>127691224</v>
       </c>
       <c r="B8" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 16206-2022 artfynd.xlsx
+++ b/artfynd/A 16206-2022 artfynd.xlsx
@@ -1365,7 +1365,7 @@
         <v>127691224</v>
       </c>
       <c r="B8" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 16206-2022 artfynd.xlsx
+++ b/artfynd/A 16206-2022 artfynd.xlsx
@@ -1365,7 +1365,7 @@
         <v>127691224</v>
       </c>
       <c r="B8" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 16206-2022 artfynd.xlsx
+++ b/artfynd/A 16206-2022 artfynd.xlsx
@@ -1365,7 +1365,7 @@
         <v>127691224</v>
       </c>
       <c r="B8" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 16206-2022 artfynd.xlsx
+++ b/artfynd/A 16206-2022 artfynd.xlsx
@@ -1365,7 +1365,7 @@
         <v>127691224</v>
       </c>
       <c r="B8" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 16206-2022 artfynd.xlsx
+++ b/artfynd/A 16206-2022 artfynd.xlsx
@@ -1365,7 +1365,7 @@
         <v>127691224</v>
       </c>
       <c r="B8" t="n">
-        <v>91317</v>
+        <v>91325</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 16206-2022 artfynd.xlsx
+++ b/artfynd/A 16206-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1457,6 +1457,250 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131488176</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57885</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sandbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>759346</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7090989</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Umeå stad</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hackspår som kådat igen</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131488089</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57885</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sandbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>759348</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7090978</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Umeå stad</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Födohack i basen, trämyror</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16206-2022 artfynd.xlsx
+++ b/artfynd/A 16206-2022 artfynd.xlsx
@@ -1462,7 +1462,7 @@
         <v>131488176</v>
       </c>
       <c r="B9" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>131488089</v>
       </c>
       <c r="B10" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 16206-2022 artfynd.xlsx
+++ b/artfynd/A 16206-2022 artfynd.xlsx
@@ -1462,7 +1462,7 @@
         <v>131488176</v>
       </c>
       <c r="B9" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>131488089</v>
       </c>
       <c r="B10" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 16206-2022 artfynd.xlsx
+++ b/artfynd/A 16206-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101211849</v>
+        <v>101211078</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>759312.7942999743</v>
+        <v>759392</v>
       </c>
       <c r="R2" t="n">
-        <v>7091279.060041744</v>
+        <v>7091023</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +756,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101211035</v>
+        <v>101210968</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759392.1135948164</v>
+        <v>759404</v>
       </c>
       <c r="R3" t="n">
-        <v>7091023.36791312</v>
+        <v>7090960</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -901,15 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101211078</v>
+        <v>101211035</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,21 +902,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -942,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759392.1135948164</v>
+        <v>759392</v>
       </c>
       <c r="R4" t="n">
-        <v>7091023.36791312</v>
+        <v>7091023</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1014,37 +999,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101210968</v>
+        <v>101211038</v>
       </c>
       <c r="B5" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>759404.8596524796</v>
+        <v>759392</v>
       </c>
       <c r="R5" t="n">
-        <v>7090960.626216589</v>
+        <v>7091023</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1127,15 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>101211038</v>
+        <v>101211849</v>
       </c>
       <c r="B6" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>759392.1135948164</v>
+        <v>759313</v>
       </c>
       <c r="R6" t="n">
-        <v>7091023.36791312</v>
+        <v>7091279</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,70 +1215,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112682705</v>
+        <v>127691224</v>
       </c>
       <c r="B7" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>bondestigen, Vb</t>
+          <t>I20-skogen, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>759330</v>
+        <v>759417</v>
       </c>
       <c r="R7" t="n">
-        <v>7091300</v>
+        <v>7091029</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,12 +1280,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,60 +1300,67 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johanna Dahl</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johanna Dahl</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127691224</v>
+        <v>104786533</v>
       </c>
       <c r="B8" t="n">
-        <v>91325</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>I20-skogen, Vb</t>
+          <t>Garnlav, Umeå, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>759417</v>
+        <v>759400</v>
       </c>
       <c r="R8" t="n">
-        <v>7091029</v>
+        <v>7090883</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,12 +1384,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2022-11-22</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,32 +1408,48 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Emil Larsson</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131488176</v>
+        <v>112682705</v>
       </c>
       <c r="B9" t="n">
-        <v>57911</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1487,22 +1470,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sandbäcken, Vb</t>
+          <t>bondestigen, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759346</v>
+        <v>759330</v>
       </c>
       <c r="R9" t="n">
-        <v>7090989</v>
+        <v>7091300</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,66 +1527,46 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hackspår som kådat igen</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Johanna Dahl</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Johanna Dahl</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131488089</v>
+        <v>131486557</v>
       </c>
       <c r="B10" t="n">
-        <v>57911</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1617,14 +1595,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sandbäcken, Vb</t>
+          <t>Hagaskolans skolskog, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759348</v>
+        <v>759405</v>
       </c>
       <c r="R10" t="n">
-        <v>7090978</v>
+        <v>7091320</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1661,7 +1639,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Födohack i basen, trämyror</t>
+          <t>Djupa födohack i basen av granen</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1700,6 +1678,491 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131488089</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sandbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>759348</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7090978</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Umeå stad</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Födohack i basen, trämyror</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131488176</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sandbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>759346</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7090989</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Umeå stad</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hackspår som kådat igen</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131488422</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hagaskolans skolskog, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>759401</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7091304</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Umeå stad</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack färska med kåda 4-5meter upp på gran invid väg</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131487630</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hagaskolans skolskog, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>759412</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7091274</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Umeå stad</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Roger Olofsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16206-2022 artfynd.xlsx
+++ b/artfynd/A 16206-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101211078</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101210968</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101211035</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101211038</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101211849</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1309,6 +1339,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127691224</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1439,6 +1474,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104786533</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1556,6 +1596,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112682705</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1678,6 +1723,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131486557</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1800,6 +1850,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131488089</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1922,6 +1977,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131488176</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2047,6 +2107,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131488422</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2163,8 +2228,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131487630</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>